--- a/reports/pdf_change_20260715.xlsx
+++ b/reports/pdf_change_20260715.xlsx
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>캡처 3/7  ·  대기: TIME, TIME, PLUS, TIGER</t>
+          <t>캡처 5/7  ·  대기: PLUS, TIGER</t>
         </is>
       </c>
     </row>
@@ -796,23 +796,23 @@
       <c r="E10" s="17" t="n"/>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>보로노이  (편출)</t>
         </is>
       </c>
       <c r="H10" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-1510320000</v>
+        <v>-1035350400</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>10.17%→11.65%</t>
+          <t>0.23%→0.00%</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>251→244</t>
+          <t>7→0</t>
         </is>
       </c>
     </row>
@@ -824,23 +824,23 @@
       <c r="E11" s="17" t="n"/>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>보로노이  (편출)</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H11" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-1035350400</v>
+        <v>-1510320000</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
-          <t>0.23%→0.00%</t>
+          <t>10.17%→11.65%</t>
         </is>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>7→0</t>
+          <t>251→244</t>
         </is>
       </c>
     </row>
@@ -897,205 +897,403 @@
       </c>
     </row>
     <row r="17" ht="19" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B17" s="20" t="n"/>
-      <c r="C17" s="20" t="n"/>
-      <c r="D17" s="20" t="n"/>
-      <c r="E17" s="20" t="n"/>
-      <c r="F17" s="20" t="n"/>
-      <c r="G17" s="20" t="n"/>
-      <c r="H17" s="20" t="n"/>
-      <c r="I17" s="20" t="n"/>
-      <c r="J17" s="20" t="n"/>
-      <c r="K17" s="20" t="n"/>
-    </row>
-    <row r="19" ht="19" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B19" s="20" t="n"/>
-      <c r="C19" s="20" t="n"/>
-      <c r="D19" s="20" t="n"/>
-      <c r="E19" s="20" t="n"/>
-      <c r="F19" s="20" t="n"/>
-      <c r="G19" s="20" t="n"/>
-      <c r="H19" s="20" t="n"/>
-      <c r="I19" s="20" t="n"/>
-      <c r="J19" s="20" t="n"/>
-      <c r="K19" s="20" t="n"/>
-    </row>
-    <row r="21" ht="19" customHeight="1">
-      <c r="A21" s="19" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,673억   ·   현금 29억(1.1%)      당일 2026-07-15  vs  전영업일 2026-07-14      매수 3종목  /  매도 2종목</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="4" t="n"/>
+      <c r="F17" s="4" t="n"/>
+      <c r="G17" s="4" t="n"/>
+      <c r="H17" s="4" t="n"/>
+      <c r="I17" s="4" t="n"/>
+      <c r="J17" s="4" t="n"/>
+      <c r="K17" s="4" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="n"/>
+      <c r="I18" s="8" t="n"/>
+      <c r="J18" s="8" t="n"/>
+      <c r="K18" s="8" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J19" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K19" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>브이엠</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="n">
+        <v>89</v>
+      </c>
+      <c r="C20" s="11" t="n">
+        <v>6992685500</v>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>1.51%→4.46%</t>
+        </is>
+      </c>
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>61→150</t>
+        </is>
+      </c>
+      <c r="G20" s="14" t="inlineStr">
+        <is>
+          <t>인텍플러스</t>
+        </is>
+      </c>
+      <c r="H20" s="15" t="n">
+        <v>-450</v>
+      </c>
+      <c r="I20" s="15" t="n">
+        <v>-12376237500</v>
+      </c>
+      <c r="J20" s="16" t="inlineStr">
+        <is>
+          <t>8.34%→3.12%</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="inlineStr">
+        <is>
+          <t>750→300</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>주성엔지니어링</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="n">
+        <v>48</v>
+      </c>
+      <c r="C21" s="11" t="n">
+        <v>6332688000</v>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>4.78%→7.48%</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>102→150</t>
+        </is>
+      </c>
+      <c r="G21" s="14" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="H21" s="15" t="n">
+        <v>-19</v>
+      </c>
+      <c r="I21" s="15" t="n">
+        <v>-3637692500</v>
+      </c>
+      <c r="J21" s="16" t="inlineStr">
+        <is>
+          <t>3.98%→2.17%</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="inlineStr">
+        <is>
+          <t>49→30</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>테스</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="C22" s="11" t="n">
+        <v>2681775000</v>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>8.13%→10.59%</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>170→188</t>
+        </is>
+      </c>
+      <c r="G22" s="17" t="n"/>
+      <c r="H22" s="17" t="n"/>
+      <c r="I22" s="17" t="n"/>
+      <c r="J22" s="17" t="n"/>
+      <c r="K22" s="17" t="n"/>
+    </row>
+    <row r="24" ht="19" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,530억   ·   현금 25억(1.0%)      당일 2026-07-15  vs  전영업일 2026-07-14      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="4" t="n"/>
+      <c r="G24" s="4" t="n"/>
+      <c r="H24" s="4" t="n"/>
+      <c r="I24" s="4" t="n"/>
+      <c r="J24" s="4" t="n"/>
+      <c r="K24" s="4" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="19" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
         <is>
           <t>■ PLUS 코스닥150액티브  (한화)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B21" s="20" t="n"/>
-      <c r="C21" s="20" t="n"/>
-      <c r="D21" s="20" t="n"/>
-      <c r="E21" s="20" t="n"/>
-      <c r="F21" s="20" t="n"/>
-      <c r="G21" s="20" t="n"/>
-      <c r="H21" s="20" t="n"/>
-      <c r="I21" s="20" t="n"/>
-      <c r="J21" s="20" t="n"/>
-      <c r="K21" s="20" t="n"/>
-    </row>
-    <row r="23" ht="19" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="B27" s="20" t="n"/>
+      <c r="C27" s="20" t="n"/>
+      <c r="D27" s="20" t="n"/>
+      <c r="E27" s="20" t="n"/>
+      <c r="F27" s="20" t="n"/>
+      <c r="G27" s="20" t="n"/>
+      <c r="H27" s="20" t="n"/>
+      <c r="I27" s="20" t="n"/>
+      <c r="J27" s="20" t="n"/>
+      <c r="K27" s="20" t="n"/>
+    </row>
+    <row r="29" ht="19" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 553억   ·   현금 9억(1.7%)      당일 2026-07-15  vs  전영업일 2026-07-14      매수 1종목  /  매도 0종목</t>
         </is>
       </c>
-      <c r="B23" s="4" t="n"/>
-      <c r="C23" s="4" t="n"/>
-      <c r="D23" s="4" t="n"/>
-      <c r="E23" s="4" t="n"/>
-      <c r="F23" s="4" t="n"/>
-      <c r="G23" s="4" t="n"/>
-      <c r="H23" s="4" t="n"/>
-      <c r="I23" s="4" t="n"/>
-      <c r="J23" s="4" t="n"/>
-      <c r="K23" s="4" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="B29" s="4" t="n"/>
+      <c r="C29" s="4" t="n"/>
+      <c r="D29" s="4" t="n"/>
+      <c r="E29" s="4" t="n"/>
+      <c r="F29" s="4" t="n"/>
+      <c r="G29" s="4" t="n"/>
+      <c r="H29" s="4" t="n"/>
+      <c r="I29" s="4" t="n"/>
+      <c r="J29" s="4" t="n"/>
+      <c r="K29" s="4" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B24" s="6" t="n"/>
-      <c r="C24" s="6" t="n"/>
-      <c r="D24" s="6" t="n"/>
-      <c r="E24" s="6" t="n"/>
-      <c r="G24" s="7" t="inlineStr">
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="6" t="n"/>
+      <c r="G30" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H24" s="8" t="n"/>
-      <c r="I24" s="8" t="n"/>
-      <c r="J24" s="8" t="n"/>
-      <c r="K24" s="8" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="9" t="inlineStr">
+      <c r="H30" s="8" t="n"/>
+      <c r="I30" s="8" t="n"/>
+      <c r="J30" s="8" t="n"/>
+      <c r="K30" s="8" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B25" s="9" t="inlineStr">
+      <c r="B31" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr">
+      <c r="C31" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D25" s="9" t="inlineStr">
+      <c r="D31" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E25" s="9" t="inlineStr">
+      <c r="E31" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G25" s="9" t="inlineStr">
+      <c r="G31" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H25" s="9" t="inlineStr">
+      <c r="H31" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I25" s="9" t="inlineStr">
+      <c r="I31" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J25" s="9" t="inlineStr">
+      <c r="J31" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K25" s="9" t="inlineStr">
+      <c r="K31" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
         <is>
           <t>큐리오시스</t>
         </is>
       </c>
-      <c r="B26" s="11" t="n">
+      <c r="B32" s="11" t="n">
         <v>296</v>
       </c>
-      <c r="C26" s="11" t="n">
+      <c r="C32" s="11" t="n">
         <v>450162720</v>
       </c>
-      <c r="D26" s="12" t="inlineStr">
+      <c r="D32" s="12" t="inlineStr">
         <is>
           <t>1.62%→1.73%</t>
         </is>
       </c>
-      <c r="E26" s="13" t="inlineStr">
+      <c r="E32" s="13" t="inlineStr">
         <is>
           <t>297→593</t>
         </is>
       </c>
-      <c r="G26" s="17" t="n"/>
-      <c r="H26" s="17" t="n"/>
-      <c r="I26" s="17" t="n"/>
-      <c r="J26" s="17" t="n"/>
-      <c r="K26" s="17" t="n"/>
-    </row>
-    <row r="28" ht="19" customHeight="1">
-      <c r="A28" s="19" t="inlineStr">
+      <c r="G32" s="17" t="n"/>
+      <c r="H32" s="17" t="n"/>
+      <c r="I32" s="17" t="n"/>
+      <c r="J32" s="17" t="n"/>
+      <c r="K32" s="17" t="n"/>
+    </row>
+    <row r="34" ht="19" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B28" s="20" t="n"/>
-      <c r="C28" s="20" t="n"/>
-      <c r="D28" s="20" t="n"/>
-      <c r="E28" s="20" t="n"/>
-      <c r="F28" s="20" t="n"/>
-      <c r="G28" s="20" t="n"/>
-      <c r="H28" s="20" t="n"/>
-      <c r="I28" s="20" t="n"/>
-      <c r="J28" s="20" t="n"/>
-      <c r="K28" s="20" t="n"/>
+      <c r="B34" s="20" t="n"/>
+      <c r="C34" s="20" t="n"/>
+      <c r="D34" s="20" t="n"/>
+      <c r="E34" s="20" t="n"/>
+      <c r="F34" s="20" t="n"/>
+      <c r="G34" s="20" t="n"/>
+      <c r="H34" s="20" t="n"/>
+      <c r="I34" s="20" t="n"/>
+      <c r="J34" s="20" t="n"/>
+      <c r="K34" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="17">
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A34:K34"/>
     <mergeCell ref="A4:E4"/>
+    <mergeCell ref="G30:K30"/>
+    <mergeCell ref="A18:E18"/>
     <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A21:K21"/>
-    <mergeCell ref="A23:K23"/>
-    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A27:K27"/>
     <mergeCell ref="A15:K15"/>
-    <mergeCell ref="G24:K24"/>
+    <mergeCell ref="A29:K29"/>
+    <mergeCell ref="A25:K25"/>
+    <mergeCell ref="A24:K24"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A19:K19"/>
-    <mergeCell ref="A28:K28"/>
     <mergeCell ref="A14:K14"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A17:K17"/>
+    <mergeCell ref="G18:K18"/>
     <mergeCell ref="G4:K4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/pdf_change_20260715.xlsx
+++ b/reports/pdf_change_20260715.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,599억   ·   현금 105억(2.3%)      당일 2026-07-15  vs  전영업일 2026-07-14      매수 1종목  /  매도 7종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,585억   ·   현금 105억(2.3%)      당일 2026-07-15  vs  전영업일 2026-07-14      매수 1종목  /  매도 7종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>74</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>952835840</v>
+        <v>947072720</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-54</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-904227840</v>
+        <v>-898758720</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>-24</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-897561600</v>
+        <v>-892132800</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         <v>-15</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-437472000</v>
+        <v>-434826000</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>-9</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-404438400</v>
+        <v>-401992200</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>-7</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-1035350400</v>
+        <v>-1029088200</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
         <v>-7</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-1510320000</v>
+        <v>-1501185000</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         <v>-3</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-368131200</v>
+        <v>-365904600</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
     <row r="14" ht="19" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,227억   ·   현금 11억(0.3%)      당일 2026-07-15  vs  전영업일 2026-07-14      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,024억   ·   현금 11억(0.3%)      당일 2026-07-15  vs  전영업일 2026-07-14      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B14" s="4" t="n"/>
@@ -899,7 +899,7 @@
     <row r="17" ht="19" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,673억   ·   현금 29억(1.1%)      당일 2026-07-15  vs  전영업일 2026-07-14      매수 3종목  /  매도 2종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,662억   ·   현금 29억(1.1%)      당일 2026-07-15  vs  전영업일 2026-07-14      매수 3종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B17" s="4" t="n"/>
@@ -995,7 +995,7 @@
         <v>89</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>6992685500</v>
+        <v>6931435700</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>-450</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-12376237500</v>
+        <v>-12267832500</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>48</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>6332688000</v>
+        <v>6277219200</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>-19</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-3637692500</v>
+        <v>-3605829500</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>18</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>2681775000</v>
+        <v>2658285000</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
     <row r="24" ht="19" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,530억   ·   현금 25억(1.0%)      당일 2026-07-15  vs  전영업일 2026-07-14      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,420억   ·   현금 25억(1.0%)      당일 2026-07-15  vs  전영업일 2026-07-14      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B24" s="4" t="n"/>
@@ -1145,7 +1145,7 @@
     <row r="29" ht="19" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 553억   ·   현금 9억(1.7%)      당일 2026-07-15  vs  전영업일 2026-07-14      매수 1종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 517억   ·   현금 9억(1.7%)      당일 2026-07-15  vs  전영업일 2026-07-14      매수 1종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B29" s="4" t="n"/>
@@ -1241,7 +1241,7 @@
         <v>296</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>450162720</v>
+        <v>442596960</v>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>

--- a/reports/pdf_change_20260715.xlsx
+++ b/reports/pdf_change_20260715.xlsx
@@ -796,23 +796,23 @@
       <c r="E10" s="17" t="n"/>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>보로노이  (편출)</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H10" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-1029088200</v>
+        <v>-1501185000</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>0.23%→0.00%</t>
+          <t>10.17%→11.65%</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>7→0</t>
+          <t>251→244</t>
         </is>
       </c>
     </row>
@@ -824,23 +824,23 @@
       <c r="E11" s="17" t="n"/>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>보로노이  (편출)</t>
         </is>
       </c>
       <c r="H11" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-1501185000</v>
+        <v>-1029088200</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
-          <t>10.17%→11.65%</t>
+          <t>0.23%→0.00%</t>
         </is>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>251→244</t>
+          <t>7→0</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_change_20260715.xlsx
+++ b/reports/pdf_change_20260715.xlsx
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>캡처 5/7  ·  대기: PLUS, TIGER</t>
+          <t>캡처 6/7  ·  대기: TIGER</t>
         </is>
       </c>
     </row>
@@ -1126,175 +1126,469 @@
       </c>
     </row>
     <row r="27" ht="19" customHeight="1">
-      <c r="A27" s="19" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B27" s="20" t="n"/>
-      <c r="C27" s="20" t="n"/>
-      <c r="D27" s="20" t="n"/>
-      <c r="E27" s="20" t="n"/>
-      <c r="F27" s="20" t="n"/>
-      <c r="G27" s="20" t="n"/>
-      <c r="H27" s="20" t="n"/>
-      <c r="I27" s="20" t="n"/>
-      <c r="J27" s="20" t="n"/>
-      <c r="K27" s="20" t="n"/>
-    </row>
-    <row r="29" ht="19" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 517억   ·   현금 9억(1.7%)      당일 2026-07-15  vs  전영업일 2026-07-14      매수 1종목  /  매도 0종목</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="n"/>
-      <c r="C29" s="4" t="n"/>
-      <c r="D29" s="4" t="n"/>
-      <c r="E29" s="4" t="n"/>
-      <c r="F29" s="4" t="n"/>
-      <c r="G29" s="4" t="n"/>
-      <c r="H29" s="4" t="n"/>
-      <c r="I29" s="4" t="n"/>
-      <c r="J29" s="4" t="n"/>
-      <c r="K29" s="4" t="n"/>
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 341억   ·   현금 2억(100.0%)      당일 2026-07-15  vs  전영업일 2026-07-14      매수 5종목  /  매도 5종목</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n"/>
+      <c r="C27" s="4" t="n"/>
+      <c r="D27" s="4" t="n"/>
+      <c r="E27" s="4" t="n"/>
+      <c r="F27" s="4" t="n"/>
+      <c r="G27" s="4" t="n"/>
+      <c r="H27" s="4" t="n"/>
+      <c r="I27" s="4" t="n"/>
+      <c r="J27" s="4" t="n"/>
+      <c r="K27" s="4" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="6" t="n"/>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="n"/>
+      <c r="I28" s="8" t="n"/>
+      <c r="J28" s="8" t="n"/>
+      <c r="K28" s="8" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G29" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H29" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I29" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J29" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K29" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="n"/>
-      <c r="C30" s="6" t="n"/>
-      <c r="D30" s="6" t="n"/>
-      <c r="E30" s="6" t="n"/>
-      <c r="G30" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H30" s="8" t="n"/>
-      <c r="I30" s="8" t="n"/>
-      <c r="J30" s="8" t="n"/>
-      <c r="K30" s="8" t="n"/>
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>인텍플러스</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="n">
+        <v>38</v>
+      </c>
+      <c r="C30" s="11" t="n">
+        <v>129684500</v>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>2.42%→2.80%</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>240→278</t>
+        </is>
+      </c>
+      <c r="G30" s="14" t="inlineStr">
+        <is>
+          <t>에이프로</t>
+        </is>
+      </c>
+      <c r="H30" s="15" t="n">
+        <v>-174</v>
+      </c>
+      <c r="I30" s="15" t="n">
+        <v>-40894350</v>
+      </c>
+      <c r="J30" s="16" t="inlineStr">
+        <is>
+          <t>0.42%→0.30%</t>
+        </is>
+      </c>
+      <c r="K30" s="13" t="inlineStr">
+        <is>
+          <t>601→427</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B31" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C31" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D31" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E31" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G31" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H31" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I31" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J31" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K31" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>에프앤가이드</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="C31" s="11" t="n">
+        <v>59045250</v>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>2.62%→2.79%</t>
+        </is>
+      </c>
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <t>495→528</t>
+        </is>
+      </c>
+      <c r="G31" s="14" t="inlineStr">
+        <is>
+          <t>액트로</t>
+        </is>
+      </c>
+      <c r="H31" s="15" t="n">
+        <v>-29</v>
+      </c>
+      <c r="I31" s="15" t="n">
+        <v>-18832600</v>
+      </c>
+      <c r="J31" s="16" t="inlineStr">
+        <is>
+          <t>0.35%→0.30%</t>
+        </is>
+      </c>
+      <c r="K31" s="13" t="inlineStr">
+        <is>
+          <t>183→154</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
+          <t>씨어스</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C32" s="11" t="n">
+        <v>53550000</v>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>5.52%→5.67%</t>
+        </is>
+      </c>
+      <c r="E32" s="13" t="inlineStr">
+        <is>
+          <t>697→717</t>
+        </is>
+      </c>
+      <c r="G32" s="14" t="inlineStr">
+        <is>
+          <t>성호전자</t>
+        </is>
+      </c>
+      <c r="H32" s="15" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I32" s="15" t="n">
+        <v>-39142500</v>
+      </c>
+      <c r="J32" s="16" t="inlineStr">
+        <is>
+          <t>0.41%→0.29%</t>
+        </is>
+      </c>
+      <c r="K32" s="13" t="inlineStr">
+        <is>
+          <t>88→63</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>서진시스템</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="C33" s="11" t="n">
+        <v>51272000</v>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>6.77%→6.91%</t>
+        </is>
+      </c>
+      <c r="E33" s="13" t="inlineStr">
+        <is>
+          <t>714→730</t>
+        </is>
+      </c>
+      <c r="G33" s="14" t="inlineStr">
+        <is>
+          <t>테스</t>
+        </is>
+      </c>
+      <c r="H33" s="15" t="n">
+        <v>-6</v>
+      </c>
+      <c r="I33" s="15" t="n">
+        <v>-110925000</v>
+      </c>
+      <c r="J33" s="16" t="inlineStr">
+        <is>
+          <t>4.16%→3.82%</t>
+        </is>
+      </c>
+      <c r="K33" s="13" t="inlineStr">
+        <is>
+          <t>76→70</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>코스메카코리아</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C34" s="11" t="n">
+        <v>34892500</v>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>0.10%→0.21%</t>
+        </is>
+      </c>
+      <c r="E34" s="13" t="inlineStr">
+        <is>
+          <t>5→10</t>
+        </is>
+      </c>
+      <c r="G34" s="14" t="inlineStr">
+        <is>
+          <t>브이엠</t>
+        </is>
+      </c>
+      <c r="H34" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I34" s="15" t="n">
+        <v>-48747500</v>
+      </c>
+      <c r="J34" s="16" t="inlineStr">
+        <is>
+          <t>4.33%→4.17%</t>
+        </is>
+      </c>
+      <c r="K34" s="13" t="inlineStr">
+        <is>
+          <t>150→145</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="19" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 517억   ·   현금 9억(1.7%)      당일 2026-07-15  vs  전영업일 2026-07-14      매수 1종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="n"/>
+      <c r="C36" s="4" t="n"/>
+      <c r="D36" s="4" t="n"/>
+      <c r="E36" s="4" t="n"/>
+      <c r="F36" s="4" t="n"/>
+      <c r="G36" s="4" t="n"/>
+      <c r="H36" s="4" t="n"/>
+      <c r="I36" s="4" t="n"/>
+      <c r="J36" s="4" t="n"/>
+      <c r="K36" s="4" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
+      <c r="E37" s="6" t="n"/>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H37" s="8" t="n"/>
+      <c r="I37" s="8" t="n"/>
+      <c r="J37" s="8" t="n"/>
+      <c r="K37" s="8" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G38" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H38" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I38" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J38" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K38" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
           <t>큐리오시스</t>
         </is>
       </c>
-      <c r="B32" s="11" t="n">
+      <c r="B39" s="11" t="n">
         <v>296</v>
       </c>
-      <c r="C32" s="11" t="n">
+      <c r="C39" s="11" t="n">
         <v>442596960</v>
       </c>
-      <c r="D32" s="12" t="inlineStr">
+      <c r="D39" s="12" t="inlineStr">
         <is>
           <t>1.62%→1.73%</t>
         </is>
       </c>
-      <c r="E32" s="13" t="inlineStr">
+      <c r="E39" s="13" t="inlineStr">
         <is>
           <t>297→593</t>
         </is>
       </c>
-      <c r="G32" s="17" t="n"/>
-      <c r="H32" s="17" t="n"/>
-      <c r="I32" s="17" t="n"/>
-      <c r="J32" s="17" t="n"/>
-      <c r="K32" s="17" t="n"/>
-    </row>
-    <row r="34" ht="19" customHeight="1">
-      <c r="A34" s="19" t="inlineStr">
+      <c r="G39" s="17" t="n"/>
+      <c r="H39" s="17" t="n"/>
+      <c r="I39" s="17" t="n"/>
+      <c r="J39" s="17" t="n"/>
+      <c r="K39" s="17" t="n"/>
+    </row>
+    <row r="41" ht="19" customHeight="1">
+      <c r="A41" s="19" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B34" s="20" t="n"/>
-      <c r="C34" s="20" t="n"/>
-      <c r="D34" s="20" t="n"/>
-      <c r="E34" s="20" t="n"/>
-      <c r="F34" s="20" t="n"/>
-      <c r="G34" s="20" t="n"/>
-      <c r="H34" s="20" t="n"/>
-      <c r="I34" s="20" t="n"/>
-      <c r="J34" s="20" t="n"/>
-      <c r="K34" s="20" t="n"/>
+      <c r="B41" s="20" t="n"/>
+      <c r="C41" s="20" t="n"/>
+      <c r="D41" s="20" t="n"/>
+      <c r="E41" s="20" t="n"/>
+      <c r="F41" s="20" t="n"/>
+      <c r="G41" s="20" t="n"/>
+      <c r="H41" s="20" t="n"/>
+      <c r="I41" s="20" t="n"/>
+      <c r="J41" s="20" t="n"/>
+      <c r="K41" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="A30:E30"/>
-    <mergeCell ref="A34:K34"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="G30:K30"/>
+  <mergeCells count="19">
+    <mergeCell ref="A15:K15"/>
+    <mergeCell ref="A24:K24"/>
+    <mergeCell ref="A36:K36"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A25:K25"/>
+    <mergeCell ref="A41:K41"/>
+    <mergeCell ref="G28:K28"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="G37:K37"/>
     <mergeCell ref="A18:E18"/>
+    <mergeCell ref="G18:K18"/>
+    <mergeCell ref="A27:K27"/>
     <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A27:K27"/>
-    <mergeCell ref="A15:K15"/>
-    <mergeCell ref="A29:K29"/>
-    <mergeCell ref="A25:K25"/>
-    <mergeCell ref="A24:K24"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A14:K14"/>
-    <mergeCell ref="A1:K1"/>
     <mergeCell ref="A17:K17"/>
-    <mergeCell ref="G18:K18"/>
     <mergeCell ref="G4:K4"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A28:E28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
